--- a/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2023_atacama.xlsx
@@ -6,36 +6,78 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Global" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Regional" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Edades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Histórico" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Histórico" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Provincial" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Histórico'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provincial'!$A$1:$B$4</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t xml:space="preserve">Categoría</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t xml:space="preserve">Región</t>
   </si>
   <si>
     <t xml:space="preserve">Valor</t>
   </si>
   <si>
+    <t xml:space="preserve">Ranking</t>
+  </si>
+  <si>
     <t xml:space="preserve">Media nacional</t>
   </si>
   <si>
-    <t xml:space="preserve">Hombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarapacá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metropolitana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antofagasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Araucanía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coquimbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ríos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica y Parinacota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magallanes</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -44,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:07</t>
+    <t xml:space="preserve">2026-07-30 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -71,24 +113,6 @@
     <t xml:space="preserve">Año</t>
   </si>
   <si>
-    <t xml:space="preserve">Tramo de edad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor regional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor nacional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 a 13 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 a 17 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 a 21 años</t>
-  </si>
-  <si>
     <t xml:space="preserve">Serie</t>
   </si>
   <si>
@@ -96,6 +120,18 @@
   </si>
   <si>
     <t xml:space="preserve">Nacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provincia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copiapó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chañaral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huasco</t>
   </si>
 </sst>
 </file>
@@ -460,9 +496,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,42 +512,236 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.95</v>
+        <v>4.42</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3.68</v>
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.09</v>
+        <v>3.51</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2.11</v>
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="C4" s="2" t="n">
+      <c r="D6" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>2.91</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C4"/>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -527,7 +758,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -535,50 +766,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -592,57 +823,167 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>0.69</v>
+      <c r="A2" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.67</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>4.39</v>
+      <c r="A3" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4.13</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>50.15</v>
+      <c r="A4" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46.92</v>
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C4"/>
+  <autoFilter ref="A1:C14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -653,167 +994,44 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>5.75</v>
+      <c r="A2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>3.59</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>5.6</v>
+      <c r="A3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2.44</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5.52</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>5.19</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>4.59</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>2.6</v>
+      <c r="A4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1.87</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C14"/>
+  <autoFilter ref="A1:B4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2023_atacama.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 10:41</t>
+    <t xml:space="preserve">2026-08-19 13:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -114,9 +114,6 @@
   </si>
   <si>
     <t xml:space="preserve">Serie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region</t>
   </si>
   <si>
     <t xml:space="preserve">Nacional</t>
@@ -844,7 +841,7 @@
         <v>2018</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>5.75</v>
@@ -855,7 +852,7 @@
         <v>2018</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>5.6</v>
@@ -866,7 +863,7 @@
         <v>2019</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>5.52</v>
@@ -877,7 +874,7 @@
         <v>2019</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>5.19</v>
@@ -888,7 +885,7 @@
         <v>2020</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>4.59</v>
@@ -899,7 +896,7 @@
         <v>2020</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>4.58</v>
@@ -910,7 +907,7 @@
         <v>2021</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>4.18</v>
@@ -921,7 +918,7 @@
         <v>2021</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>4.08</v>
@@ -932,7 +929,7 @@
         <v>2022</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>3.05</v>
@@ -943,7 +940,7 @@
         <v>2023</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>3.04</v>
@@ -954,7 +951,7 @@
         <v>2023</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>2.91</v>
@@ -965,7 +962,7 @@
         <v>2024</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>2.84</v>
@@ -976,7 +973,7 @@
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>2.6</v>
@@ -1000,7 +997,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -1008,7 +1005,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>3.59</v>
@@ -1016,7 +1013,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2.44</v>
@@ -1024,7 +1021,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1.87</v>

--- a/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2023_atacama.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:53</t>
+    <t xml:space="preserve">2026-08-28 11:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2023_atacama.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_e_rezmat_a_2023_atacama.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:05</t>
+    <t xml:space="preserve">2026-09-06 18:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
